--- a/docentes/Sanchez Hernández Raymundo - Estadisticos 20232.xlsx
+++ b/docentes/Sanchez Hernández Raymundo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -687,16 +705,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>76.67</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +731,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.95999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -733,16 +757,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -756,16 +783,19 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -779,16 +809,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -802,16 +835,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -867,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>86.67</v>
+        <v>76.67</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,7 +938,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -919,16 +955,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -945,16 +981,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -971,13 +1007,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -997,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1016,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1048,24 +1084,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920205</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920188</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920314</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Sanchez Hernández Raymundo - Estadisticos 20232.xlsx
+++ b/docentes/Sanchez Hernández Raymundo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,33 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -903,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>76.67</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -929,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>86.95999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -964,7 +937,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -981,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1016,7 +989,7 @@
         <v>96</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1033,16 +1006,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1052,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1082,75 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920177</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920188</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920314</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
